--- a/export/Приложение_В.xlsx
+++ b/export/Приложение_В.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -614,88 +614,88 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>38.091</v>
+        <v>45.565</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>56.736</v>
+        <v>61.175</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>18.645</v>
+        <v>15.611</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37.073</v>
+        <v>44.676</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>56.818</v>
+        <v>60.537</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>19.745</v>
+        <v>15.861</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-0.2081</v>
+        <v>-0.9318</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-2.4458</v>
+        <v>-3.2887</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>27.311</v>
+        <v>25.977</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>31.397</v>
+        <v>29.425</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8.458</v>
+        <v>9.435</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9.206</v>
+        <v>10.276</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>51.539</v>
+        <v>57.622</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>50.325</v>
+        <v>56.1</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>163.9657</v>
+        <v>155.3402</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>145.7688</v>
+        <v>142.348</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>102.4786</v>
+        <v>97.08759999999999</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>81.9829</v>
+        <v>77.67010000000001</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>111.7825</v>
+        <v>154.78</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>80.24339999999999</v>
+        <v>113.4688</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.9167999999999999</v>
+        <v>0.6273</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1.0217</v>
+        <v>0.6845</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>63.221</v>
+        <v>69.325</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>49.422</v>
+        <v>54.609</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>12.644</v>
+        <v>13.865</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>9.884</v>
+        <v>10.922</v>
       </c>
     </row>
     <row r="3">
@@ -703,88 +703,88 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>36.096</v>
+        <v>42.477</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>55.171</v>
+        <v>59.943</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>19.075</v>
+        <v>17.467</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>35</v>
+        <v>41.487</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>55.621</v>
+        <v>59.788</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20.621</v>
+        <v>18.301</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.1129</v>
+        <v>-0.5886</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-1.9961</v>
+        <v>-2.8631</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>26.825</v>
+        <v>27.02</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>31.09</v>
+        <v>30.858</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>7.863</v>
+        <v>8.965</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8.474</v>
+        <v>9.694000000000001</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>49.621</v>
+        <v>55.398</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>48.549</v>
+        <v>54.052</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>127.5718</v>
+        <v>129.3557</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>113.2862</v>
+        <v>117.1632</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>82.54649999999999</v>
+        <v>83.45529999999999</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>65.8822</v>
+        <v>66.621</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>78.9789</v>
+        <v>109.1527</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>54.8297</v>
+        <v>77.9422</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>1.0452</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>1.2016</v>
+        <v>0.8547</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>48.631</v>
+        <v>56.356</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>37.789</v>
+        <v>44.133</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>9.726000000000001</v>
+        <v>11.271</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>7.558</v>
+        <v>8.827</v>
       </c>
     </row>
     <row r="4">
@@ -792,88 +792,88 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>34.605</v>
+        <v>40.184</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>54.17</v>
+        <v>59.013</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>19.566</v>
+        <v>18.829</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33.44</v>
+        <v>39.11</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>54.784</v>
+        <v>59.034</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>21.344</v>
+        <v>19.924</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.405</v>
+        <v>-0.2885</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-1.7444</v>
+        <v>-2.5504</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>26.606</v>
+        <v>27.724</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>31.339</v>
+        <v>31.875</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7.446</v>
+        <v>8.606</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8.250999999999999</v>
+        <v>9.401</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>48.313</v>
+        <v>53.758</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>47.365</v>
+        <v>52.497</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>99.0005</v>
+        <v>104.9707</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>88.6437</v>
+        <v>95.26739999999999</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>66.4028</v>
+        <v>69.98050000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>52.8643</v>
+        <v>55.7366</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>57.1452</v>
+        <v>79.108</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>40.5948</v>
+        <v>56.8844</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>1.162</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>1.3022</v>
+        <v>0.9798</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>37.711</v>
+        <v>45.155</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>29.132</v>
+        <v>35.159</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>7.542</v>
+        <v>9.031000000000001</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>5.826</v>
+        <v>7.032</v>
       </c>
     </row>
     <row r="5">
@@ -881,88 +881,88 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>33.735</v>
+        <v>38.609</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>52.675</v>
+        <v>57.529</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>18.94</v>
+        <v>18.92</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32.496</v>
+        <v>37.45</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>53.43</v>
+        <v>57.686</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20.933</v>
+        <v>20.237</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.4665</v>
+        <v>-0.14</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-1.5664</v>
+        <v>-2.3455</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>25.646</v>
+        <v>27.368</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>30.35</v>
+        <v>31.624</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7.172</v>
+        <v>8.308</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7.851</v>
+        <v>9.042</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>47.025</v>
+        <v>52.153</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>46.105</v>
+        <v>50.916</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>78.2869</v>
+        <v>85.5642</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>70.9997</v>
+        <v>78.33159999999999</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>54.5035</v>
+        <v>59.0098</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43.2741</v>
+        <v>46.8845</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>45.9327</v>
+        <v>62.5099</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>31.5075</v>
+        <v>44.155</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>1.1866</v>
+        <v>0.944</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>1.3735</v>
+        <v>1.0618</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>30.269</v>
+        <v>36.822</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>23.249</v>
+        <v>28.509</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>6.054</v>
+        <v>7.364</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>4.65</v>
+        <v>5.702</v>
       </c>
     </row>
     <row r="6">
@@ -970,88 +970,88 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>32.978</v>
+        <v>37.203</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>51.443</v>
+        <v>56.191</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18.465</v>
+        <v>18.988</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.664</v>
+        <v>35.96</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>52.328</v>
+        <v>56.474</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20.664</v>
+        <v>20.514</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.5463</v>
+        <v>0.0644</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-1.4247</v>
+        <v>-2.1299</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>24.826</v>
+        <v>26.798</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>29.662</v>
+        <v>31.33</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6.907</v>
+        <v>7.875</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7.574</v>
+        <v>8.686</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>45.937</v>
+        <v>50.666</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>45.07</v>
+        <v>49.495</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>63.7124</v>
+        <v>71.09910000000001</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>58.3683</v>
+        <v>65.5886</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>46.1077</v>
+        <v>50.7851</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>36.5019</v>
+        <v>40.2448</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>37.8385</v>
+        <v>49.5098</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>25.5236</v>
+        <v>35.0548</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>1.2185</v>
+        <v>1.0258</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>1.4301</v>
+        <v>1.1481</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>25.097</v>
+        <v>30.707</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>19.161</v>
+        <v>23.633</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>5.019</v>
+        <v>6.141</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>3.832</v>
+        <v>4.727</v>
       </c>
     </row>
     <row r="7">
@@ -1059,88 +1059,88 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>32.297</v>
+        <v>35.916</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>50.386</v>
+        <v>54.953</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>18.089</v>
+        <v>19.038</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>30.907</v>
+        <v>34.588</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>51.395</v>
+        <v>55.359</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20.488</v>
+        <v>20.771</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.602</v>
+        <v>0.2085</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-1.2321</v>
+        <v>-1.9037</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>24.207</v>
+        <v>26.457</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>28.969</v>
+        <v>31.015</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6.72</v>
+        <v>7.628</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7.249</v>
+        <v>8.340999999999999</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>45.003</v>
+        <v>49.353</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>44.159</v>
+        <v>48.192</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>53.0241</v>
+        <v>60.0781</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>48.9781</v>
+        <v>55.7989</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>39.9497</v>
+        <v>44.5023</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>31.5279</v>
+        <v>35.1676</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>32.1965</v>
+        <v>41.077</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>20.9188</v>
+        <v>28.3944</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>1.2408</v>
+        <v>1.0834</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>1.5072</v>
+        <v>1.2385</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>116</v>
+        <v>80</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>21.345</v>
+        <v>26.105</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>16.194</v>
+        <v>19.964</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>4.269</v>
+        <v>5.221</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>3.239</v>
+        <v>3.993</v>
       </c>
     </row>
     <row r="8">
@@ -1148,88 +1148,88 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>31.671</v>
+        <v>34.715</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>49.449</v>
+        <v>53.784</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>17.778</v>
+        <v>19.068</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>30.205</v>
+        <v>33.303</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>50.58</v>
+        <v>54.312</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>20.375</v>
+        <v>21.009</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.6851</v>
+        <v>0.363</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-1.0581</v>
+        <v>-1.631</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>23.596</v>
+        <v>26.074</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>28.424</v>
+        <v>30.579</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6.504</v>
+        <v>7.369</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6.991</v>
+        <v>7.939</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>44.155</v>
+        <v>48.115</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>43.359</v>
+        <v>46.961</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>44.9321</v>
+        <v>51.5198</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>41.7898</v>
+        <v>48.142</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>35.3038</v>
+        <v>39.6306</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>27.767</v>
+        <v>31.2241</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>27.7102</v>
+        <v>34.6056</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>17.6101</v>
+        <v>23.17</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>1.274</v>
+        <v>1.1452</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>1.5768</v>
+        <v>1.3476</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>18.536</v>
+        <v>22.57</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>13.969</v>
+        <v>17.144</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>3.707</v>
+        <v>4.514</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>2.794</v>
+        <v>3.429</v>
       </c>
     </row>
     <row r="9">
@@ -1237,88 +1237,88 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>31.088</v>
+        <v>33.581</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>48.596</v>
+        <v>52.657</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>17.509</v>
+        <v>19.075</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>29.543</v>
+        <v>32.083</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>49.849</v>
+        <v>53.309</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>20.306</v>
+        <v>21.226</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.7924</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0.8895</v>
+        <v>-1.3502</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>22.98</v>
+        <v>25.522</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>27.962</v>
+        <v>30.146</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6.264</v>
+        <v>7.017</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6.767</v>
+        <v>7.569</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>43.37</v>
+        <v>46.913</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>42.635</v>
+        <v>45.806</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>38.6475</v>
+        <v>44.7642</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>36.1554</v>
+        <v>42.06</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>31.7255</v>
+        <v>35.8114</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>24.861</v>
+        <v>28.1241</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>24.0897</v>
+        <v>29.1613</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>15.1203</v>
+        <v>19.2644</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1.317</v>
+        <v>1.228</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>1.6442</v>
+        <v>1.4599</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>16.381</v>
+        <v>19.808</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>12.258</v>
+        <v>14.938</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>3.276</v>
+        <v>3.962</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>2.452</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="10">
@@ -1326,88 +1326,88 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>30.656</v>
+        <v>32.5</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>48.356</v>
+        <v>51.554</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>17.7</v>
+        <v>19.054</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>29.03</v>
+        <v>30.914</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>49.48</v>
+        <v>52.335</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>20.45</v>
+        <v>21.421</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.8645</v>
+        <v>0.7517</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0.6741</v>
+        <v>-1.0555</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23.064</v>
+        <v>25.04</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>27.666</v>
+        <v>29.694</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.229</v>
+        <v>6.738</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6.542</v>
+        <v>7.218</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>43.053</v>
+        <v>45.772</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>42.189</v>
+        <v>44.706</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>33.6632</v>
+        <v>39.3558</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>31.874</v>
+        <v>37.1644</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>28.9293</v>
+        <v>32.7965</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>22.579</v>
+        <v>25.6668</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>21.4963</v>
+        <v>25.2145</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>13.0488</v>
+        <v>16.2675</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>1.3458</v>
+        <v>1.3007</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>1.7303</v>
+        <v>1.5778</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>14.751</v>
+        <v>17.622</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>10.957</v>
+        <v>13.187</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>2.95</v>
+        <v>3.524</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>2.191</v>
+        <v>2.637</v>
       </c>
     </row>
     <row r="11">
@@ -1415,88 +1415,88 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>30.009</v>
+        <v>31.461</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>47.806</v>
+        <v>50.461</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>17.797</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>28.293</v>
+        <v>29.787</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>49.108</v>
+        <v>51.376</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>20.815</v>
+        <v>21.589</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9729</v>
+        <v>0.9546</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0.2787</v>
+        <v>-0.7156</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>22.944</v>
+        <v>24.482</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>27.283</v>
+        <v>29.144</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.12</v>
+        <v>6.437</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6.19</v>
+        <v>6.84</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>42.454</v>
+        <v>44.657</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>41.656</v>
+        <v>43.644</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>30.0847</v>
+        <v>34.9729</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>28.5806</v>
+        <v>33.1783</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>27.1256</v>
+        <v>30.4112</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>21.0785</v>
+        <v>23.7104</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>19.5269</v>
+        <v>22.0075</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>11.1613</v>
+        <v>13.8353</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1.3891</v>
+        <v>1.3819</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>1.8885</v>
+        <v>1.7138</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>220</v>
+        <v>169</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>13.567</v>
+        <v>15.872</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>9.991</v>
+        <v>11.779</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>2.713</v>
+        <v>3.174</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>1.998</v>
+        <v>2.356</v>
       </c>
     </row>
     <row r="12">
@@ -1504,88 +1504,88 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>28.995</v>
+        <v>30.544</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>44.829</v>
+        <v>49.823</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>15.833</v>
+        <v>19.279</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28.631</v>
+        <v>28.778</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>49.73</v>
+        <v>50.681</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>21.1</v>
+        <v>21.903</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>0.8004</v>
+        <v>1.1522</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-0.2525</v>
+        <v>-0.1464</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>20.844</v>
+        <v>24.389</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>27.563</v>
+        <v>28.323</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.812</v>
+        <v>6.262</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6.211</v>
+        <v>6.274</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>40.218</v>
+        <v>43.891</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>42.16</v>
+        <v>42.794</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>27.0764</v>
+        <v>31.3837</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>25.8751</v>
+        <v>30.0481</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>25.6759</v>
+        <v>28.5307</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>19.856</v>
+        <v>22.1532</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>19.4492</v>
+        <v>19.5297</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>10.456</v>
+        <v>11.4107</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>1.3202</v>
+        <v>1.4609</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>1.899</v>
+        <v>1.9414</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>12.446</v>
+        <v>14.499</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>9.513999999999999</v>
+        <v>10.665</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>2.489</v>
+        <v>2.9</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>1.903</v>
+        <v>2.133</v>
       </c>
     </row>
     <row r="13">
@@ -1593,88 +1593,177 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>27.698</v>
+        <v>29.089</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>41.203</v>
+        <v>46.336</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13.505</v>
+        <v>17.247</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>29.434</v>
+        <v>28.64</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>49.611</v>
+        <v>50.924</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>20.177</v>
+        <v>22.284</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>0.6312</v>
+        <v>1.1307</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-2.4927</v>
+        <v>0.0545</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>18.202</v>
+        <v>21.878</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>32.869</v>
+        <v>28.38</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.328</v>
+        <v>5.761</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>10.2</v>
+        <v>6.151</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>37.43</v>
+        <v>41.158</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>43.376</v>
+        <v>42.884</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>24.6737</v>
+        <v>28.7125</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>24.1892</v>
+        <v>27.6761</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>24.6737</v>
+        <v>27.3452</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>18.9798</v>
+        <v>21.138</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>19.7</v>
+        <v>18.8293</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>18.9243</v>
+        <v>10.455</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1.2525</v>
+        <v>1.4523</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>1.0029</v>
+        <v>2.0218</v>
       </c>
       <c r="X13" s="2" t="n">
         <v>124</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>129</v>
+        <v>223</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>11.468</v>
+        <v>13.294</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>9.327</v>
+        <v>10.131</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>2.294</v>
+        <v>2.659</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>1.865</v>
+        <v>2.026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>27.381</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>42.116</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>14.735</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>28.945</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>50.831</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>21.886</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1.0759</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>-2.4899</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>18.772</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>35.211</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>5.113</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>10.835</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>37.843</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>44.06</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>26.6398</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>26.224</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>26.6398</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>20.4922</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>18.6247</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>20.4099</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>1.4303</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="Y14" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>12.252</v>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>9.917999999999999</v>
+      </c>
+      <c r="AB14" s="2" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>1.984</v>
       </c>
     </row>
   </sheetData>

--- a/export/Приложение_В.xlsx
+++ b/export/Приложение_В.xlsx
@@ -614,88 +614,88 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45.565</v>
+        <v>38.272</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>61.175</v>
+        <v>59.144</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>15.611</v>
+        <v>20.873</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>44.676</v>
+        <v>37.187</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>60.537</v>
+        <v>59.336</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>15.861</v>
+        <v>22.15</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>-0.9318</v>
+        <v>0.0165</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-3.2887</v>
+        <v>-2.172</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>25.977</v>
+        <v>29.406</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>29.425</v>
+        <v>33.497</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>9.435</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>10.276</v>
+        <v>9.175000000000001</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>57.622</v>
+        <v>52.991</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>56.1</v>
+        <v>51.763</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>155.3402</v>
+        <v>192.8878</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>142.348</v>
+        <v>171.3431</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>97.08759999999999</v>
+        <v>120.5548</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>77.67010000000001</v>
+        <v>96.4439</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>154.78</v>
+        <v>119.7663</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>113.4688</v>
+        <v>85.2582</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.6273</v>
+        <v>1.0066</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.6845</v>
+        <v>1.1312</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>69.325</v>
+        <v>74.67100000000001</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>54.609</v>
+        <v>58.292</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>13.865</v>
+        <v>14.934</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>10.922</v>
+        <v>11.658</v>
       </c>
     </row>
     <row r="3">
@@ -703,88 +703,88 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>42.477</v>
+        <v>36.259</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>59.943</v>
+        <v>57.394</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>17.467</v>
+        <v>21.136</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>41.487</v>
+        <v>35.099</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>59.788</v>
+        <v>57.928</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>18.301</v>
+        <v>22.829</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>-0.5886</v>
+        <v>0.2658</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-2.8631</v>
+        <v>-1.7982</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>27.02</v>
+        <v>29.013</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>30.858</v>
+        <v>33.276</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>8.965</v>
+        <v>8.143000000000001</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>9.694000000000001</v>
+        <v>8.648999999999999</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>55.398</v>
+        <v>51.031</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>54.052</v>
+        <v>49.939</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>129.3557</v>
+        <v>149.7984</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>117.1632</v>
+        <v>133.4194</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>83.45529999999999</v>
+        <v>96.64409999999999</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>66.621</v>
+        <v>77.1494</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>109.1527</v>
+        <v>87.35590000000001</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>77.9422</v>
+        <v>60.2382</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0.7645999999999999</v>
+        <v>1.1063</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>0.8547</v>
+        <v>1.2807</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>56.356</v>
+        <v>57.158</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>44.133</v>
+        <v>44.361</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>11.271</v>
+        <v>11.432</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>8.827</v>
+        <v>8.872</v>
       </c>
     </row>
     <row r="4">
@@ -792,88 +792,88 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>40.184</v>
+        <v>34.742</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>59.013</v>
+        <v>56.231</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>18.829</v>
+        <v>21.489</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>39.11</v>
+        <v>33.517</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>59.034</v>
+        <v>56.923</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>19.924</v>
+        <v>23.406</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>-0.2885</v>
+        <v>0.5817</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-2.5504</v>
+        <v>-1.5547</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>27.724</v>
+        <v>28.561</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>31.875</v>
+        <v>33.382</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>8.606</v>
+        <v>7.654</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9.401</v>
+        <v>8.420999999999999</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>53.758</v>
+        <v>49.604</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>52.497</v>
+        <v>48.654</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>104.9707</v>
+        <v>117.0405</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>95.26739999999999</v>
+        <v>105.1574</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>69.98050000000001</v>
+        <v>78.027</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>55.7366</v>
+        <v>62.1454</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>79.108</v>
+        <v>63.2977</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>56.8844</v>
+        <v>45.0945</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>0.8846000000000001</v>
+        <v>1.2327</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>0.9798</v>
+        <v>1.3781</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>45.155</v>
+        <v>44.466</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>35.159</v>
+        <v>34.316</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>9.031000000000001</v>
+        <v>8.893000000000001</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>7.032</v>
+        <v>6.863</v>
       </c>
     </row>
     <row r="5">
@@ -881,88 +881,88 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>38.609</v>
+        <v>33.88</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>57.529</v>
+        <v>54.536</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>18.92</v>
+        <v>20.656</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>37.45</v>
+        <v>32.583</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>57.686</v>
+        <v>55.367</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>20.237</v>
+        <v>22.785</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>-0.14</v>
+        <v>0.6402</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-2.3455</v>
+        <v>-1.3555</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27.368</v>
+        <v>27.363</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>31.624</v>
+        <v>32.095</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>8.308</v>
+        <v>7.347</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>9.042</v>
+        <v>7.955</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>52.153</v>
+        <v>48.201</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>50.916</v>
+        <v>47.275</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>85.5642</v>
+        <v>93.2744</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>78.33159999999999</v>
+        <v>84.8668</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>59.0098</v>
+        <v>64.3271</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>46.8845</v>
+        <v>51.1092</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>62.5099</v>
+        <v>51.2124</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>44.155</v>
+        <v>35.0596</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.944</v>
+        <v>1.2561</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>1.0618</v>
+        <v>1.4578</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>36.822</v>
+        <v>35.859</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>28.509</v>
+        <v>27.523</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>7.364</v>
+        <v>7.172</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>5.702</v>
+        <v>5.505</v>
       </c>
     </row>
     <row r="6">
@@ -970,88 +970,88 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37.203</v>
+        <v>33.131</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>56.191</v>
+        <v>53.158</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>18.988</v>
+        <v>20.027</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>35.96</v>
+        <v>31.762</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>56.474</v>
+        <v>54.118</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>20.514</v>
+        <v>22.357</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.0644</v>
+        <v>0.7318</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-2.1299</v>
+        <v>-1.1886</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>26.798</v>
+        <v>26.327</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>31.33</v>
+        <v>31.161</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>7.875</v>
+        <v>7.032</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8.686</v>
+        <v>7.616</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>50.666</v>
+        <v>47.026</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>49.495</v>
+        <v>46.154</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>71.09910000000001</v>
+        <v>76.4592</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>65.5886</v>
+        <v>70.24809999999999</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>50.7851</v>
+        <v>54.6137</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>40.2448</v>
+        <v>43.2788</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>49.5098</v>
+        <v>42.2474</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>35.0548</v>
+        <v>28.3876</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>1.0258</v>
+        <v>1.2927</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>1.1481</v>
+        <v>1.5246</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>30.707</v>
+        <v>29.849</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>23.633</v>
+        <v>22.781</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>6.141</v>
+        <v>5.97</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>4.727</v>
+        <v>4.556</v>
       </c>
     </row>
     <row r="7">
@@ -1059,88 +1059,88 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>35.916</v>
+        <v>32.461</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>54.953</v>
+        <v>51.995</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>19.038</v>
+        <v>19.533</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>34.588</v>
+        <v>31.019</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>55.359</v>
+        <v>53.078</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>20.771</v>
+        <v>22.059</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.2085</v>
+        <v>0.7944</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-1.9037</v>
+        <v>-1.035</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>26.457</v>
+        <v>25.55</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>31.015</v>
+        <v>30.437</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>7.628</v>
+        <v>6.811</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8.340999999999999</v>
+        <v>7.344</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>49.353</v>
+        <v>46.031</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>48.192</v>
+        <v>45.203</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>60.0781</v>
+        <v>64.0369</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>55.7989</v>
+        <v>59.2991</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>44.5023</v>
+        <v>47.4348</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>35.1676</v>
+        <v>37.485</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>41.077</v>
+        <v>35.9969</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>28.3944</v>
+        <v>23.6352</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>1.0834</v>
+        <v>1.3177</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>1.2385</v>
+        <v>1.586</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>26.105</v>
+        <v>25.46</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>19.964</v>
+        <v>19.317</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>5.221</v>
+        <v>5.092</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>3.993</v>
+        <v>3.863</v>
       </c>
     </row>
     <row r="8">
@@ -1148,88 +1148,88 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>34.715</v>
+        <v>31.849</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>53.784</v>
+        <v>50.98</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>19.068</v>
+        <v>19.131</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>33.303</v>
+        <v>30.333</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>54.312</v>
+        <v>52.184</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>21.009</v>
+        <v>21.85</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.363</v>
+        <v>0.8442</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-1.631</v>
+        <v>-0.8843</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>26.074</v>
+        <v>24.925</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>30.579</v>
+        <v>29.844</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>7.369</v>
+        <v>6.638</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7.939</v>
+        <v>7.109</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>48.115</v>
+        <v>45.156</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>46.961</v>
+        <v>44.371</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>51.5198</v>
+        <v>54.5614</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>48.142</v>
+        <v>50.8555</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>39.6306</v>
+        <v>41.9703</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>31.2241</v>
+        <v>33.0675</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>34.6056</v>
+        <v>31.375</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>23.17</v>
+        <v>20.0864</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>1.1452</v>
+        <v>1.3377</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>1.3476</v>
+        <v>1.6463</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>22.57</v>
+        <v>22.147</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>17.144</v>
+        <v>16.7</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>4.514</v>
+        <v>4.429</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>3.429</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="9">
@@ -1237,88 +1237,88 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>33.581</v>
+        <v>31.281</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>52.657</v>
+        <v>50.073</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>19.075</v>
+        <v>18.792</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>32.083</v>
+        <v>29.691</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>53.309</v>
+        <v>51.396</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>21.226</v>
+        <v>21.705</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.9319</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-1.3502</v>
+        <v>-0.6975</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>25.522</v>
+        <v>24.281</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>30.146</v>
+        <v>29.252</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>7.017</v>
+        <v>6.421</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7.569</v>
+        <v>6.85</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>46.913</v>
+        <v>44.353</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>45.806</v>
+        <v>43.62</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>44.7642</v>
+        <v>47.1496</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>42.06</v>
+        <v>44.191</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>35.8114</v>
+        <v>37.7197</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>28.1241</v>
+        <v>29.6228</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>29.1613</v>
+        <v>27.477</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>19.2644</v>
+        <v>17.2126</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1.228</v>
+        <v>1.3728</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>1.4599</v>
+        <v>1.721</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>19.808</v>
+        <v>19.585</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>14.938</v>
+        <v>14.673</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>3.962</v>
+        <v>3.917</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>2.988</v>
+        <v>2.935</v>
       </c>
     </row>
     <row r="10">
@@ -1326,88 +1326,88 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>32.5</v>
+        <v>30.747</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>51.554</v>
+        <v>49.243</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>19.054</v>
+        <v>18.496</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>30.914</v>
+        <v>29.082</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>52.335</v>
+        <v>50.686</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>21.421</v>
+        <v>21.604</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>0.7517</v>
+        <v>1.0138</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-1.0555</v>
+        <v>-0.5088</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25.04</v>
+        <v>23.713</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>29.694</v>
+        <v>28.727</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.738</v>
+        <v>6.231</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7.218</v>
+        <v>6.615</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>45.772</v>
+        <v>43.617</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>44.706</v>
+        <v>42.937</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>39.3558</v>
+        <v>41.2325</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>37.1644</v>
+        <v>38.83</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>32.7965</v>
+        <v>34.3604</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>25.6668</v>
+        <v>26.8907</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>25.2145</v>
+        <v>24.447</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>16.2675</v>
+        <v>14.9684</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>1.3007</v>
+        <v>1.4055</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>1.5778</v>
+        <v>1.7965</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>17.622</v>
+        <v>17.567</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>13.187</v>
+        <v>13.071</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>3.524</v>
+        <v>3.513</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>2.637</v>
+        <v>2.614</v>
       </c>
     </row>
     <row r="11">
@@ -1415,88 +1415,88 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>31.461</v>
+        <v>30.241</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>50.461</v>
+        <v>48.472</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>19</v>
+        <v>18.231</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>29.787</v>
+        <v>28.5</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>51.376</v>
+        <v>50.035</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>21.589</v>
+        <v>21.535</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>0.9546</v>
+        <v>1.096</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0.7156</v>
+        <v>-0.3125</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24.482</v>
+        <v>23.188</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>29.144</v>
+        <v>28.239</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.437</v>
+        <v>6.053</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6.84</v>
+        <v>6.392</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>44.657</v>
+        <v>42.93</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>43.644</v>
+        <v>42.307</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>34.9729</v>
+        <v>36.4275</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>33.1783</v>
+        <v>34.4483</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>30.4112</v>
+        <v>31.6761</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>23.7104</v>
+        <v>24.6966</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>22.0075</v>
+        <v>22.0218</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>13.8353</v>
+        <v>13.1716</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1.3819</v>
+        <v>1.4384</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>1.7138</v>
+        <v>1.875</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>15.872</v>
+        <v>15.953</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>11.779</v>
+        <v>11.784</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>3.174</v>
+        <v>3.191</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>2.356</v>
+        <v>2.357</v>
       </c>
     </row>
     <row r="12">
@@ -1504,88 +1504,88 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>30.544</v>
+        <v>29.857</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>49.823</v>
+        <v>48.249</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>19.279</v>
+        <v>18.392</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28.778</v>
+        <v>28.036</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>50.681</v>
+        <v>49.71</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>21.903</v>
+        <v>21.674</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.1522</v>
+        <v>1.1831</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-0.1464</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>24.389</v>
+        <v>23.202</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>28.323</v>
+        <v>27.59</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>6.262</v>
+        <v>5.993</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6.274</v>
+        <v>6.006</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>43.891</v>
+        <v>42.641</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>42.794</v>
+        <v>41.92</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>31.3837</v>
+        <v>32.469</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>30.0481</v>
+        <v>30.9729</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>28.5307</v>
+        <v>29.5173</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>22.1532</v>
+        <v>22.9193</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>19.5297</v>
+        <v>20.0356</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>11.4107</v>
+        <v>11.2584</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>1.4609</v>
+        <v>1.4732</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>1.9414</v>
+        <v>2.0357</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>14.499</v>
+        <v>14.695</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>10.665</v>
+        <v>10.773</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>2.9</v>
+        <v>2.939</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>2.133</v>
+        <v>2.155</v>
       </c>
     </row>
     <row r="13">
@@ -1593,88 +1593,88 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>29.089</v>
+        <v>28.889</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>46.336</v>
+        <v>45.25</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>17.247</v>
+        <v>16.361</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>28.64</v>
+        <v>28.404</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>50.924</v>
+        <v>50.366</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>22.284</v>
+        <v>21.962</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.1307</v>
+        <v>1.0177</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.0545</v>
+        <v>0.0718</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21.878</v>
+        <v>20.999</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>28.38</v>
+        <v>27.962</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.761</v>
+        <v>5.656</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6.151</v>
+        <v>6.071</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>41.158</v>
+        <v>40.407</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>42.884</v>
+        <v>42.456</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>28.7125</v>
+        <v>29.4767</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>27.6761</v>
+        <v>28.2986</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>27.3452</v>
+        <v>28.0731</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>21.138</v>
+        <v>21.7007</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>18.8293</v>
+        <v>19.9513</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>10.455</v>
+        <v>10.6968</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1.4523</v>
+        <v>1.4071</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>2.0218</v>
+        <v>2.0287</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>13.294</v>
+        <v>13.563</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>10.131</v>
+        <v>10.323</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>2.659</v>
+        <v>2.713</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>2.026</v>
+        <v>2.065</v>
       </c>
     </row>
     <row r="14">
@@ -1682,88 +1682,88 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>27.381</v>
+        <v>27.635</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>42.116</v>
+        <v>41.57</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>14.735</v>
+        <v>13.935</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>28.945</v>
+        <v>29.231</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>50.831</v>
+        <v>50.103</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>21.886</v>
+        <v>20.872</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>1.0759</v>
+        <v>0.8215</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-2.4899</v>
+        <v>-2.4891</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18.772</v>
+        <v>18.304</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>35.211</v>
+        <v>33.813</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5.113</v>
+        <v>5.191</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10.835</v>
+        <v>10.453</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>37.843</v>
+        <v>37.609</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>44.06</v>
+        <v>43.649</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>26.6398</v>
+        <v>27.1205</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>26.224</v>
+        <v>26.8064</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>26.6398</v>
+        <v>27.1205</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>20.4922</v>
+        <v>20.8619</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>18.6247</v>
+        <v>20.413</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>20.4099</v>
+        <v>20.7716</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>1.4303</v>
+        <v>1.3286</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>1.004</v>
+        <v>1.0043</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>12.252</v>
+        <v>12.58</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>9.917999999999999</v>
+        <v>10.188</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>2.45</v>
+        <v>2.516</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>1.984</v>
+        <v>2.038</v>
       </c>
     </row>
   </sheetData>

--- a/export/Приложение_В.xlsx
+++ b/export/Приложение_В.xlsx
@@ -632,28 +632,28 @@
         <v>22.15</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.0165</v>
+        <v>0.1737</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-2.172</v>
+        <v>-1.9261</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>29.406</v>
+        <v>28.832</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>33.497</v>
+        <v>32.655</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>8.132999999999999</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>9.175000000000001</v>
+        <v>8.579000000000001</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>52.991</v>
+        <v>52.861</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>51.763</v>
+        <v>51.588</v>
       </c>
       <c r="P2" s="2" t="n">
         <v>192.8878</v>
@@ -665,37 +665,37 @@
         <v>120.5548</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>96.4439</v>
+        <v>120.5548</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>119.7663</v>
+        <v>112.7212</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>85.2582</v>
+        <v>98.04689999999999</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>1.0066</v>
+        <v>1.0695</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1.1312</v>
+        <v>1.2296</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>74.67100000000001</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>58.292</v>
+        <v>72.86499999999999</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>14.934</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>11.658</v>
+        <v>14.573</v>
       </c>
     </row>
     <row r="3">
@@ -721,28 +721,28 @@
         <v>22.829</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.2658</v>
+        <v>0.4586</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-1.7982</v>
+        <v>-1.7493</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>29.013</v>
+        <v>28.378</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>33.276</v>
+        <v>33.122</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>8.143000000000001</v>
+        <v>7.701</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8.648999999999999</v>
+        <v>8.544</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>51.031</v>
+        <v>50.906</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>49.939</v>
+        <v>49.911</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>149.7984</v>
@@ -751,40 +751,40 @@
         <v>133.4194</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>96.64409999999999</v>
+        <v>95.1101</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>77.1494</v>
+        <v>95.1101</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>87.35590000000001</v>
+        <v>80.3674</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>60.2382</v>
+        <v>73.1464</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>1.1063</v>
+        <v>1.1834</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>1.2807</v>
+        <v>1.3003</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>57.158</v>
+        <v>56.251</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>44.361</v>
+        <v>54.688</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>11.432</v>
+        <v>11.25</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>8.872</v>
+        <v>10.938</v>
       </c>
     </row>
     <row r="4">
@@ -810,28 +810,28 @@
         <v>23.406</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.5817</v>
+        <v>0.6631</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-1.5547</v>
+        <v>-1.4373</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.561</v>
+        <v>28.316</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>33.382</v>
+        <v>33.04</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7.654</v>
+        <v>7.49</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8.420999999999999</v>
+        <v>8.196999999999999</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>49.604</v>
+        <v>49.563</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>48.654</v>
+        <v>48.6</v>
       </c>
       <c r="P4" s="2" t="n">
         <v>117.0405</v>
@@ -840,40 +840,40 @@
         <v>105.1574</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>78.027</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>62.1454</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>63.2977</v>
+        <v>59.6806</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>45.0945</v>
+        <v>52.9861</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>1.2327</v>
+        <v>1.2652</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>1.3781</v>
+        <v>1.4251</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>44.466</v>
+        <v>43.032</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>34.316</v>
+        <v>41.696</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>8.893000000000001</v>
+        <v>8.606</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>6.863</v>
+        <v>8.339</v>
       </c>
     </row>
     <row r="5">
@@ -899,28 +899,28 @@
         <v>22.785</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.6402</v>
+        <v>0.699</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-1.3555</v>
+        <v>-1.3421</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27.363</v>
+        <v>27.19</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>32.095</v>
+        <v>32.058</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7.347</v>
+        <v>7.233</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7.955</v>
+        <v>7.931</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>48.201</v>
+        <v>48.174</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>47.275</v>
+        <v>47.27</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>93.2744</v>
@@ -929,40 +929,40 @@
         <v>84.8668</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>64.3271</v>
+        <v>61.1635</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>51.1092</v>
+        <v>61.1635</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>51.2124</v>
+        <v>47.7983</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>35.0596</v>
+        <v>41.8018</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>1.2561</v>
+        <v>1.2796</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>1.4578</v>
+        <v>1.4632</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>35.859</v>
+        <v>34.096</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>27.523</v>
+        <v>32.938</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>7.172</v>
+        <v>6.819</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>5.505</v>
+        <v>6.588</v>
       </c>
     </row>
     <row r="6">
@@ -988,28 +988,28 @@
         <v>22.357</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.7318</v>
+        <v>0.8064</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-1.1886</v>
+        <v>-1.2016</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>26.327</v>
+        <v>26.118</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>31.161</v>
+        <v>31.195</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>7.032</v>
+        <v>6.897</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7.616</v>
+        <v>7.637</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>47.026</v>
+        <v>46.996</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>46.154</v>
+        <v>46.158</v>
       </c>
       <c r="P6" s="2" t="n">
         <v>76.4592</v>
@@ -1018,40 +1018,40 @@
         <v>70.24809999999999</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>54.6137</v>
+        <v>50.9728</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>43.2788</v>
+        <v>50.9728</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>42.2474</v>
+        <v>38.5415</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>28.3876</v>
+        <v>33.549</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>1.2927</v>
+        <v>1.3225</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>1.5246</v>
+        <v>1.5194</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>29.849</v>
+        <v>27.859</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>22.781</v>
+        <v>26.832</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>5.97</v>
+        <v>5.572</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>4.556</v>
+        <v>5.366</v>
       </c>
     </row>
     <row r="7">
@@ -1077,25 +1077,25 @@
         <v>22.059</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.7944</v>
+        <v>0.8556</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-1.035</v>
+        <v>-1.0362</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25.55</v>
+        <v>25.382</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>30.437</v>
+        <v>30.44</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6.811</v>
+        <v>6.704</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7.344</v>
+        <v>7.345</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46.031</v>
+        <v>46.008</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>45.203</v>
@@ -1107,40 +1107,40 @@
         <v>59.2991</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>47.4348</v>
+        <v>43.4149</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>37.485</v>
+        <v>43.4149</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>35.9969</v>
+        <v>32.345</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>23.6352</v>
+        <v>27.3823</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>1.3177</v>
+        <v>1.3422</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>1.586</v>
+        <v>1.5855</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>25.46</v>
+        <v>23.302</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>19.317</v>
+        <v>22.373</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>5.092</v>
+        <v>4.66</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>3.863</v>
+        <v>4.475</v>
       </c>
     </row>
     <row r="8">
@@ -1166,28 +1166,28 @@
         <v>21.85</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8442</v>
+        <v>0.8731</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0.8843</v>
+        <v>-0.8555</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24.925</v>
+        <v>24.847</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>29.844</v>
+        <v>29.773</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6.638</v>
+        <v>6.589</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7.109</v>
+        <v>7.067</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>45.156</v>
+        <v>45.146</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>44.371</v>
+        <v>44.365</v>
       </c>
       <c r="P8" s="2" t="n">
         <v>54.5614</v>
@@ -1196,40 +1196,40 @@
         <v>50.8555</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>41.9703</v>
+        <v>37.6285</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>33.0675</v>
+        <v>37.6285</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>31.375</v>
+        <v>27.8889</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>20.0864</v>
+        <v>22.6976</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>1.3377</v>
+        <v>1.3492</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>1.6463</v>
+        <v>1.6578</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>22.147</v>
+        <v>19.856</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>16.7</v>
+        <v>19.004</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>4.429</v>
+        <v>3.971</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>3.34</v>
+        <v>3.801</v>
       </c>
     </row>
     <row r="9">
@@ -1255,28 +1255,28 @@
         <v>21.705</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.9319</v>
+        <v>0.9457</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0.6975</v>
+        <v>-0.664</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.281</v>
+        <v>24.245</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>29.252</v>
+        <v>29.174</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6.421</v>
+        <v>6.399</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6.85</v>
+        <v>6.805</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>44.353</v>
+        <v>44.349</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>43.62</v>
+        <v>43.614</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>47.1496</v>
@@ -1285,40 +1285,40 @@
         <v>44.191</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>37.7197</v>
+        <v>33.0874</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>29.6228</v>
+        <v>33.0874</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>27.477</v>
+        <v>24.0062</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>17.2126</v>
+        <v>19.0774</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1.3728</v>
+        <v>1.3783</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>1.721</v>
+        <v>1.7344</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>19.585</v>
+        <v>17.18</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>14.673</v>
+        <v>16.389</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>3.917</v>
+        <v>3.436</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>2.935</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="10">
@@ -1344,28 +1344,28 @@
         <v>21.604</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.0138</v>
+        <v>1.0565</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0.5088</v>
+        <v>-0.4643</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23.713</v>
+        <v>23.605</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>28.727</v>
+        <v>28.627</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.231</v>
+        <v>6.165</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6.615</v>
+        <v>6.559</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>43.617</v>
+        <v>43.606</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>42.937</v>
+        <v>42.931</v>
       </c>
       <c r="P10" s="2" t="n">
         <v>41.2325</v>
@@ -1374,40 +1374,40 @@
         <v>38.83</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>34.3604</v>
+        <v>29.4518</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>26.8907</v>
+        <v>29.4518</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>24.447</v>
+        <v>20.7029</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>14.9684</v>
+        <v>16.2334</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>1.4055</v>
+        <v>1.4226</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>1.7965</v>
+        <v>1.8143</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>17.567</v>
+        <v>15.057</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>13.071</v>
+        <v>14.315</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>3.513</v>
+        <v>3.011</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>2.614</v>
+        <v>2.863</v>
       </c>
     </row>
     <row r="11">
@@ -1433,28 +1433,28 @@
         <v>21.535</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.096</v>
+        <v>1.1377</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0.3125</v>
+        <v>-0.2573</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23.188</v>
+        <v>23.084</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>28.239</v>
+        <v>28.119</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>6.053</v>
+        <v>5.991</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6.392</v>
+        <v>6.327</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>42.93</v>
+        <v>42.92</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>42.307</v>
+        <v>42.302</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>36.4275</v>
@@ -1463,40 +1463,40 @@
         <v>34.4483</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>31.6761</v>
+        <v>26.4928</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>24.6966</v>
+        <v>26.4928</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>22.0218</v>
+        <v>18.207</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>13.1716</v>
+        <v>13.9651</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1.4384</v>
+        <v>1.4551</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>1.875</v>
+        <v>1.8971</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>15.953</v>
+        <v>13.343</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>11.784</v>
+        <v>12.641</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>3.191</v>
+        <v>2.669</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>2.357</v>
+        <v>2.528</v>
       </c>
     </row>
     <row r="12">
@@ -1522,28 +1522,28 @@
         <v>21.674</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.1831</v>
+        <v>1.1996</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.0814</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23.202</v>
+        <v>23.162</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>27.59</v>
+        <v>27.606</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.993</v>
+        <v>5.969</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6.006</v>
+        <v>6.014</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>42.641</v>
+        <v>42.637</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>41.92</v>
+        <v>41.921</v>
       </c>
       <c r="P12" s="2" t="n">
         <v>32.469</v>
@@ -1552,40 +1552,40 @@
         <v>30.9729</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>29.5173</v>
+        <v>24.0511</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>22.9193</v>
+        <v>24.0511</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>20.0356</v>
+        <v>16.2527</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>11.2584</v>
+        <v>11.8328</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>1.4732</v>
+        <v>1.4798</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>2.0357</v>
+        <v>2.0326</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="Y12" s="2" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>14.695</v>
+        <v>11.973</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>10.773</v>
+        <v>11.305</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>2.939</v>
+        <v>2.395</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>2.155</v>
+        <v>2.261</v>
       </c>
     </row>
     <row r="13">
@@ -1611,25 +1611,25 @@
         <v>21.962</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.0177</v>
+        <v>1.0326</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.0718</v>
+        <v>0.1031</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20.999</v>
+        <v>20.963</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>27.962</v>
+        <v>27.898</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.656</v>
+        <v>5.634</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6.071</v>
+        <v>6.039</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>40.407</v>
+        <v>40.403</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>42.456</v>
@@ -1641,40 +1641,40 @@
         <v>28.2986</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>28.0731</v>
+        <v>22.2466</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>21.7007</v>
+        <v>22.2466</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>19.9513</v>
+        <v>15.7439</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>10.6968</v>
+        <v>10.8986</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1.4071</v>
+        <v>1.413</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>2.0287</v>
+        <v>2.0412</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>13.563</v>
+        <v>10.748</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>10.323</v>
+        <v>10.582</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>2.713</v>
+        <v>2.15</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>2.065</v>
+        <v>2.116</v>
       </c>
     </row>
     <row r="14">
@@ -1700,28 +1700,28 @@
         <v>20.872</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.8215</v>
+        <v>0.869</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-2.4891</v>
+        <v>-2.4665</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18.304</v>
+        <v>18.187</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>33.813</v>
+        <v>33.713</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5.191</v>
+        <v>5.121</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10.453</v>
+        <v>10.375</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>37.609</v>
+        <v>37.598</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>43.649</v>
+        <v>43.621</v>
       </c>
       <c r="P14" s="2" t="n">
         <v>27.1205</v>
@@ -1730,37 +1730,37 @@
         <v>26.8064</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>27.1205</v>
+        <v>20.8619</v>
       </c>
       <c r="S14" s="2" t="n">
         <v>20.8619</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>20.413</v>
+        <v>15.481</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>20.7716</v>
+        <v>20.5861</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>1.3286</v>
+        <v>1.3476</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>1.0043</v>
+        <v>1.0134</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>12.58</v>
+        <v>9.677</v>
       </c>
       <c r="AA14" s="2" t="n">
         <v>10.188</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>2.516</v>
+        <v>1.935</v>
       </c>
       <c r="AC14" s="2" t="n">
         <v>2.038</v>

--- a/export/Приложение_В.xlsx
+++ b/export/Приложение_В.xlsx
@@ -614,88 +614,88 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>38.272</v>
+        <v>40.882</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>59.144</v>
+        <v>59.675</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>20.873</v>
+        <v>18.793</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37.187</v>
+        <v>39.87</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>59.336</v>
+        <v>59.529</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>22.15</v>
+        <v>19.658</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.1737</v>
+        <v>-0.1426</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-1.9261</v>
+        <v>-2.5523</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>28.832</v>
+        <v>27.025</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>32.655</v>
+        <v>31.461</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>8.132999999999999</v>
+        <v>8.089</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>8.579000000000001</v>
+        <v>9.250999999999999</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>52.861</v>
+        <v>54.252</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>51.588</v>
+        <v>53.049</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>192.8878</v>
+        <v>174.6905</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>171.3431</v>
+        <v>157.0796</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>120.5548</v>
+        <v>109.1816</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>120.5548</v>
+        <v>109.1816</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>112.7212</v>
+        <v>115.7875</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>98.04689999999999</v>
+        <v>111.5147</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>1.0695</v>
+        <v>0.9429</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1.2296</v>
+        <v>0.9791</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>17</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>74.67100000000001</v>
+        <v>71.459</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>72.86499999999999</v>
+        <v>69.991</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>14.934</v>
+        <v>14.292</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>14.573</v>
+        <v>13.998</v>
       </c>
     </row>
     <row r="3">
@@ -703,88 +703,88 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>36.259</v>
+        <v>38.493</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>57.394</v>
+        <v>58.101</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>21.136</v>
+        <v>19.609</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>35.099</v>
+        <v>37.397</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>57.928</v>
+        <v>58.359</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>22.829</v>
+        <v>20.961</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.4586</v>
+        <v>-0.0143</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-1.7493</v>
+        <v>-2.2378</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>28.378</v>
+        <v>27.82</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>33.122</v>
+        <v>32.177</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>7.701</v>
+        <v>8.196999999999999</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8.544</v>
+        <v>8.978</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>50.906</v>
+        <v>52.388</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>49.911</v>
+        <v>51.248</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>149.7984</v>
+        <v>139.4687</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>133.4194</v>
+        <v>124.9834</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>95.1101</v>
+        <v>88.55159999999999</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>95.1101</v>
+        <v>88.55159999999999</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>80.3674</v>
+        <v>89.06059999999999</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>73.1464</v>
+        <v>80.1469</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>1.1834</v>
+        <v>0.9943</v>
       </c>
       <c r="W3" s="2" t="n">
-        <v>1.3003</v>
+        <v>1.1049</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>56.251</v>
+        <v>55.116</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>54.688</v>
+        <v>53.781</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>11.25</v>
+        <v>11.023</v>
       </c>
       <c r="AC3" s="2" t="n">
-        <v>10.938</v>
+        <v>10.756</v>
       </c>
     </row>
     <row r="4">
@@ -792,88 +792,88 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>34.742</v>
+        <v>36.709</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>56.231</v>
+        <v>57.014</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>21.489</v>
+        <v>20.304</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>33.517</v>
+        <v>35.541</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>56.923</v>
+        <v>57.439</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>23.406</v>
+        <v>21.898</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.6631</v>
+        <v>0.2734</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-1.4373</v>
+        <v>-1.8485</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.316</v>
+        <v>27.859</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>33.04</v>
+        <v>32.214</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>7.49</v>
+        <v>7.829</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>8.196999999999999</v>
+        <v>8.468</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>49.563</v>
+        <v>50.913</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>48.6</v>
+        <v>49.8</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>117.0405</v>
+        <v>110.498</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>105.1574</v>
+        <v>99.65779999999999</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>75.51000000000001</v>
+        <v>71.289</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>75.51000000000001</v>
+        <v>71.289</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>59.6806</v>
+        <v>64.2608</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>52.9861</v>
+        <v>56.5522</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>1.2652</v>
+        <v>1.1094</v>
       </c>
       <c r="W4" s="2" t="n">
-        <v>1.4251</v>
+        <v>1.2606</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z4" s="2" t="n">
-        <v>43.032</v>
+        <v>42.614</v>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>41.696</v>
+        <v>41.439</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>8.606</v>
+        <v>8.523</v>
       </c>
       <c r="AC4" s="2" t="n">
-        <v>8.339</v>
+        <v>8.288</v>
       </c>
     </row>
     <row r="5">
@@ -881,88 +881,88 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>33.88</v>
+        <v>35.601</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>54.536</v>
+        <v>55.393</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>20.656</v>
+        <v>19.792</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>32.583</v>
+        <v>34.357</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>55.367</v>
+        <v>55.961</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>22.785</v>
+        <v>21.604</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.699</v>
+        <v>0.3745</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-1.3421</v>
+        <v>-1.6899</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27.19</v>
+        <v>26.933</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>32.058</v>
+        <v>31.438</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>7.233</v>
+        <v>7.515</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7.931</v>
+        <v>8.144</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>48.174</v>
+        <v>49.442</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>47.27</v>
+        <v>48.386</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>93.2744</v>
+        <v>88.8176</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>84.8668</v>
+        <v>81.0164</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>61.1635</v>
+        <v>58.241</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>61.1635</v>
+        <v>58.241</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>47.7983</v>
+        <v>50.6525</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>41.8018</v>
+        <v>43.9879</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>1.2796</v>
+        <v>1.1498</v>
       </c>
       <c r="W5" s="2" t="n">
-        <v>1.4632</v>
+        <v>1.324</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>34.096</v>
+        <v>33.905</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>32.938</v>
+        <v>32.868</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>6.819</v>
+        <v>6.781</v>
       </c>
       <c r="AC5" s="2" t="n">
-        <v>6.588</v>
+        <v>6.574</v>
       </c>
     </row>
     <row r="6">
@@ -970,88 +970,88 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>33.131</v>
+        <v>34.626</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>53.158</v>
+        <v>54.024</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>20.027</v>
+        <v>19.398</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>31.762</v>
+        <v>33.305</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>54.118</v>
+        <v>54.722</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>22.357</v>
+        <v>21.417</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.8064</v>
+        <v>0.4118</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-1.2016</v>
+        <v>-1.6187</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>26.118</v>
+        <v>26.362</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>31.195</v>
+        <v>31.064</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>6.897</v>
+        <v>7.376</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7.637</v>
+        <v>8.028</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>46.996</v>
+        <v>48.219</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>46.158</v>
+        <v>47.218</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>76.4592</v>
+        <v>73.2153</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>70.24809999999999</v>
+        <v>67.3938</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>50.9728</v>
+        <v>48.8102</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>50.9728</v>
+        <v>48.8102</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>38.5415</v>
+        <v>41.907</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>33.549</v>
+        <v>36.088</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>1.3225</v>
+        <v>1.1647</v>
       </c>
       <c r="W6" s="2" t="n">
-        <v>1.5194</v>
+        <v>1.3525</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="Z6" s="2" t="n">
-        <v>27.859</v>
+        <v>27.735</v>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>26.832</v>
+        <v>26.802</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>5.572</v>
+        <v>5.547</v>
       </c>
       <c r="AC6" s="2" t="n">
-        <v>5.366</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="7">
@@ -1059,88 +1059,88 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>32.461</v>
+        <v>33.743</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>51.995</v>
+        <v>52.826</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>19.533</v>
+        <v>19.083</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>31.019</v>
+        <v>32.345</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>53.078</v>
+        <v>53.65</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>22.059</v>
+        <v>21.304</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.8556</v>
+        <v>0.6021</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-1.0362</v>
+        <v>-1.4091</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25.382</v>
+        <v>25.428</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>30.44</v>
+        <v>30.389</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>6.704</v>
+        <v>6.947</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7.345</v>
+        <v>7.675</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>46.008</v>
+        <v>47.059</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>45.203</v>
+        <v>46.131</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>64.0369</v>
+        <v>61.5723</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>59.2991</v>
+        <v>57.1047</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>43.4149</v>
+        <v>41.7439</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>43.4149</v>
+        <v>41.7439</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>32.345</v>
+        <v>33.6421</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>27.3823</v>
+        <v>29.0622</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>1.3422</v>
+        <v>1.2408</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>1.5855</v>
+        <v>1.4364</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>23.302</v>
+        <v>23.188</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>22.373</v>
+        <v>22.334</v>
       </c>
       <c r="AB7" s="2" t="n">
-        <v>4.66</v>
+        <v>4.638</v>
       </c>
       <c r="AC7" s="2" t="n">
-        <v>4.475</v>
+        <v>4.467</v>
       </c>
     </row>
     <row r="8">
@@ -1148,88 +1148,88 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>31.849</v>
+        <v>32.928</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>50.98</v>
+        <v>51.747</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>19.131</v>
+        <v>18.819</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>30.333</v>
+        <v>31.452</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>52.184</v>
+        <v>52.695</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>21.85</v>
+        <v>21.242</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.8731</v>
+        <v>0.6448</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0.8555</v>
+        <v>-1.1955</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>24.847</v>
+        <v>25.008</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>29.773</v>
+        <v>29.795</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>6.589</v>
+        <v>6.834</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7.067</v>
+        <v>7.357</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>45.146</v>
+        <v>46.077</v>
       </c>
       <c r="O8" s="2" t="n">
-        <v>44.365</v>
+        <v>45.154</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>54.5614</v>
+        <v>52.6372</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>50.8555</v>
+        <v>49.1307</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>37.6285</v>
+        <v>36.3015</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>37.6285</v>
+        <v>36.3015</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>27.8889</v>
+        <v>28.858</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>22.6976</v>
+        <v>23.8542</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>1.3492</v>
+        <v>1.2579</v>
       </c>
       <c r="W8" s="2" t="n">
-        <v>1.6578</v>
+        <v>1.5218</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Y8" s="2" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Z8" s="2" t="n">
-        <v>19.856</v>
+        <v>19.733</v>
       </c>
       <c r="AA8" s="2" t="n">
-        <v>19.004</v>
+        <v>18.942</v>
       </c>
       <c r="AB8" s="2" t="n">
-        <v>3.971</v>
+        <v>3.947</v>
       </c>
       <c r="AC8" s="2" t="n">
-        <v>3.801</v>
+        <v>3.788</v>
       </c>
     </row>
     <row r="9">
@@ -1237,88 +1237,88 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>31.281</v>
+        <v>32.164</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>50.073</v>
+        <v>50.752</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>18.792</v>
+        <v>18.588</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>29.691</v>
+        <v>30.61</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>51.396</v>
+        <v>51.824</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>21.705</v>
+        <v>21.214</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>0.9457</v>
+        <v>0.7361</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0.664</v>
+        <v>-0.978</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.245</v>
+        <v>24.493</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>29.174</v>
+        <v>29.259</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>6.399</v>
+        <v>6.641</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6.805</v>
+        <v>7.067</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>44.349</v>
+        <v>45.147</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>43.614</v>
+        <v>44.262</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>47.1496</v>
+        <v>45.6242</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>44.191</v>
+        <v>42.8202</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>33.0874</v>
+        <v>32.0169</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>33.0874</v>
+        <v>32.0169</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>24.0062</v>
+        <v>24.7342</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>19.0774</v>
+        <v>19.9012</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>1.3783</v>
+        <v>1.2944</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>1.7344</v>
+        <v>1.6088</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>17.18</v>
+        <v>17.044</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>16.389</v>
+        <v>16.303</v>
       </c>
       <c r="AB9" s="2" t="n">
-        <v>3.436</v>
+        <v>3.409</v>
       </c>
       <c r="AC9" s="2" t="n">
-        <v>3.278</v>
+        <v>3.261</v>
       </c>
     </row>
     <row r="10">
@@ -1326,88 +1326,88 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>30.747</v>
+        <v>31.441</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>49.243</v>
+        <v>49.818</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>18.496</v>
+        <v>18.377</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>29.082</v>
+        <v>29.808</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>50.686</v>
+        <v>51.016</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>21.604</v>
+        <v>21.208</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.0565</v>
+        <v>0.8619</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-0.4643</v>
+        <v>-0.7561</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23.605</v>
+        <v>23.916</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>28.627</v>
+        <v>28.763</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>6.165</v>
+        <v>6.401</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6.559</v>
+        <v>6.799</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>43.606</v>
+        <v>44.261</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>42.931</v>
+        <v>43.433</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>41.2325</v>
+        <v>40.0163</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>38.83</v>
+        <v>37.7387</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>29.4518</v>
+        <v>28.583</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>29.4518</v>
+        <v>28.583</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>20.7029</v>
+        <v>21.2554</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>16.2334</v>
+        <v>16.8377</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>1.4226</v>
+        <v>1.3447</v>
       </c>
       <c r="W10" s="2" t="n">
-        <v>1.8143</v>
+        <v>1.6976</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Y10" s="2" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="Z10" s="2" t="n">
-        <v>15.057</v>
+        <v>14.909</v>
       </c>
       <c r="AA10" s="2" t="n">
-        <v>14.315</v>
+        <v>14.208</v>
       </c>
       <c r="AB10" s="2" t="n">
-        <v>3.011</v>
+        <v>2.982</v>
       </c>
       <c r="AC10" s="2" t="n">
-        <v>2.863</v>
+        <v>2.842</v>
       </c>
     </row>
     <row r="11">
@@ -1415,88 +1415,88 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>30.241</v>
+        <v>30.75</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>48.472</v>
+        <v>48.927</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>18.231</v>
+        <v>18.177</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>28.5</v>
+        <v>29.037</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>50.035</v>
+        <v>50.252</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>21.535</v>
+        <v>21.215</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1.1377</v>
+        <v>1.0137</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-0.2573</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>23.084</v>
+        <v>23.297</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>28.119</v>
+        <v>28.291</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>5.991</v>
+        <v>6.134</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6.327</v>
+        <v>6.547</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>42.92</v>
+        <v>43.412</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>42.302</v>
+        <v>42.654</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>36.4275</v>
+        <v>35.4611</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>34.4483</v>
+        <v>33.5862</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>26.4928</v>
+        <v>25.7899</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>26.4928</v>
+        <v>25.7899</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>18.207</v>
+        <v>18.3496</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>13.9651</v>
+        <v>14.4198</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1.4551</v>
+        <v>1.4055</v>
       </c>
       <c r="W11" s="2" t="n">
-        <v>1.8971</v>
+        <v>1.7885</v>
       </c>
       <c r="X11" s="2" t="n">
         <v>127</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>13.343</v>
+        <v>13.186</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>12.641</v>
+        <v>12.518</v>
       </c>
       <c r="AB11" s="2" t="n">
-        <v>2.669</v>
+        <v>2.637</v>
       </c>
       <c r="AC11" s="2" t="n">
-        <v>2.528</v>
+        <v>2.504</v>
       </c>
     </row>
     <row r="12">
@@ -1504,88 +1504,88 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>29.857</v>
+        <v>30.18</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>48.249</v>
+        <v>48.537</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>18.392</v>
+        <v>18.357</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>28.036</v>
+        <v>28.383</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>49.71</v>
+        <v>49.783</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>21.674</v>
+        <v>21.4</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1.1996</v>
+        <v>1.1364</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0.0814</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23.162</v>
+        <v>23.254</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>27.606</v>
+        <v>27.574</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>5.969</v>
+        <v>6.034</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6.014</v>
+        <v>6.099</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>42.637</v>
+        <v>42.944</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>41.921</v>
+        <v>42.095</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>32.469</v>
+        <v>31.7113</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>30.9729</v>
+        <v>30.2959</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>24.0511</v>
+        <v>23.4899</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>24.0511</v>
+        <v>23.4899</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>16.2527</v>
+        <v>16.1492</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>11.8328</v>
+        <v>11.9235</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>1.4798</v>
+        <v>1.4546</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>2.0326</v>
+        <v>1.97</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Y12" s="2" t="n">
         <v>196</v>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>11.973</v>
+        <v>11.809</v>
       </c>
       <c r="AA12" s="2" t="n">
-        <v>11.305</v>
+        <v>11.166</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>2.395</v>
+        <v>2.362</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>2.261</v>
+        <v>2.233</v>
       </c>
     </row>
     <row r="13">
@@ -1593,88 +1593,88 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>28.889</v>
+        <v>29.039</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>45.25</v>
+        <v>45.39</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>16.361</v>
+        <v>16.35</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>28.404</v>
+        <v>28.58</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>50.366</v>
+        <v>50.291</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>21.962</v>
+        <v>21.711</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1.0326</v>
+        <v>0.9811</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0.1031</v>
+        <v>0.0075</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20.963</v>
+        <v>21.069</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>27.898</v>
+        <v>27.776</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>5.634</v>
+        <v>5.7</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>6.039</v>
+        <v>6.073</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>40.403</v>
+        <v>40.555</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>42.456</v>
+        <v>42.475</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>29.4767</v>
+        <v>28.8805</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>28.2986</v>
+        <v>27.7689</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>22.2466</v>
+        <v>21.7966</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>22.2466</v>
+        <v>21.7966</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>15.7439</v>
+        <v>15.6536</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>10.8986</v>
+        <v>10.8821</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1.413</v>
+        <v>1.3924</v>
       </c>
       <c r="W13" s="2" t="n">
-        <v>2.0412</v>
+        <v>2.003</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>10.748</v>
+        <v>10.58</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>10.582</v>
+        <v>10.427</v>
       </c>
       <c r="AB13" s="2" t="n">
-        <v>2.15</v>
+        <v>2.116</v>
       </c>
       <c r="AC13" s="2" t="n">
-        <v>2.116</v>
+        <v>2.085</v>
       </c>
     </row>
     <row r="14">
@@ -1682,88 +1682,88 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>27.635</v>
+        <v>27.622</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>41.57</v>
+        <v>41.557</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>13.935</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29.231</v>
+        <v>29.233</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>50.103</v>
+        <v>50.086</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>20.872</v>
+        <v>20.853</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>0.869</v>
+        <v>0.8733</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-2.4665</v>
+        <v>-2.4853</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>18.187</v>
+        <v>18.177</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>33.713</v>
+        <v>33.772</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>5.121</v>
+        <v>5.115</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>10.375</v>
+        <v>10.433</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>37.598</v>
+        <v>37.584</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>43.621</v>
+        <v>43.633</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>27.1205</v>
+        <v>26.6572</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>26.8064</v>
+        <v>26.3049</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>20.8619</v>
+        <v>20.5056</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>20.8619</v>
+        <v>20.5056</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>15.481</v>
+        <v>15.197</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>20.5861</v>
+        <v>20.386</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>1.3476</v>
+        <v>1.3493</v>
       </c>
       <c r="W14" s="2" t="n">
-        <v>1.0134</v>
+        <v>1.0059</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Y14" s="2" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Z14" s="2" t="n">
-        <v>9.677</v>
+        <v>9.507</v>
       </c>
       <c r="AA14" s="2" t="n">
-        <v>10.188</v>
+        <v>10.014</v>
       </c>
       <c r="AB14" s="2" t="n">
-        <v>1.935</v>
+        <v>1.901</v>
       </c>
       <c r="AC14" s="2" t="n">
-        <v>2.038</v>
+        <v>2.003</v>
       </c>
     </row>
   </sheetData>

--- a/export/Приложение_В.xlsx
+++ b/export/Приложение_В.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Приложение В" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приложение В" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/export/Приложение_В.xlsx
+++ b/export/Приложение_В.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приложение В" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Приложение В" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
